--- a/data/so-good-apartments/project/sources_uses.xlsx
+++ b/data/so-good-apartments/project/sources_uses.xlsx
@@ -7,17 +7,21 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources Uses" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources Uses'!$A$1:$K$55</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,15 +30,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+        <bgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -46,19 +81,52 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,210 +493,1938 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Sources &amp; Uses of Funds – So-Good Apartments</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Sub-Category</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Percentage_of_Total_Project_Cost</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senior Loan</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>$18000000</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>60.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>General Partner Equity</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>GP Equity Contribution</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.07690000000000001</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Developer's direct equity contribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Sponsor Equity</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Hoque Global</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>$11300000</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>37.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Limited Partner Equity</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>LP Equity Contribution</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Institutional investor equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Gap Financing</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>City Grant</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>$500000</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Acquisition</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>$6000000</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>20.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>$18550000</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>62.2%</t>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Debt</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Senior Construction Loan</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Construction Loan Draw</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Funded based on construction progress</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Acquisition Costs</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Land Acquisition</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Land Purchase Price</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>0.1231</v>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Cost to acquire the development site</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Acquisition Costs</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Due Diligence</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Environmental Site Assessment (Phase I/II)</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Environmental reports and testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Acquisition Costs</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Due Diligence</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Geotechnical Investigation</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Soil testing and foundation recommendations</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Acquisition Costs</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Legal &amp; Title</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Title Insurance &amp; Escrow Fees</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Cost for title policy and closing services</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Acquisition Costs</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Legal &amp; Title</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Land Acquisition Legal Fees</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Legal services for property purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Site Work</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Site Demolition &amp; Clearing</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Removal of existing structures and vegetation</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Site Work</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Mass Grading &amp; Earthwork</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Preparation of site for foundations and infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Site Work</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Site Utilities (Water</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Sewer</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Electric</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Gas)</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Installation of new utility lines and connections</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Building Structure</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Concrete Foundations &amp; Slab</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0.07690000000000001</v>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Concrete footings</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>foundation walls</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>and floor slabs</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Building Structure</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Structural Framing (Wood/Steel)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.07690000000000001</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Primary structural elements for the buildings</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Building Envelope</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Exterior Walls &amp; Siding</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Façade materials</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>insulation</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>and finishes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Building Envelope</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Roofing System</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Installation of full roofing system</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Building Envelope</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Windows &amp; Doors (Exterior)</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Installation of all exterior windows and entrance doors</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Mechanical Systems</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>HVAC System Installation</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Heating</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>ventilation</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>and air conditioning systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Plumbing Systems</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Plumbing System Installation</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>fixtures</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>and hot water systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Electrical Systems</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Electrical System Installation</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Wiring</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>lighting</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>and power distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Unit Interior Finishes</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Kitchen Cabinets</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Counters &amp; Appliances</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Kitchen finishes for all 300 units</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Unit Interior Finishes</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Bathroom Vanities &amp; Fixtures</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Bathroom finishes for all 300 units</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Unit Interior Finishes</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Flooring &amp; Paint</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Interior flooring and paint finishes for all units</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Common Areas &amp; Amenities</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Lobbies &amp; Common Area Finishes</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Interior finishes for lobby</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>corridors</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>and shared spaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Common Areas &amp; Amenities</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Amenity Spaces (Gym</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Clubroom)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Build-out of fitness center</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>resident lounge</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Common Areas &amp; Amenities</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Pool &amp; Deck Construction</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Outdoor swimming pool and surrounding deck</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Site Improvements</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Parking Structure/Surface Parking</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Construction of parking facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Site Improvements</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Exterior Lighting &amp; Signage</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Site lighting and wayfinding signage</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Site Improvements</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Landscaping &amp; Irrigation</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Installation of greenery</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>pathways</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>and irrigation system</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Site Improvements</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Fencing &amp; Gates</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Perimeter fencing and access gates</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Soft Costs</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>$3630000</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>12.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Financing</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>$1620000</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>5.5%</t>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Architecture &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Architectural Design Fees</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Fees for lead architect and design team</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Architecture &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Structural Engineering Fees</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Fees for structural design</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Architecture &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>MEP Engineering Fees</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Fees for mechanical</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>electrical</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>plumbing design</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Architecture &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Civil Engineering Fees</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Fees for site and infrastructure design</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Legal &amp; Professional</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Development Legal Fees</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Legal services for project contracts</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>agreements</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Permits &amp; Fees</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Zoning &amp; Entitlement Fees</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Fees for zoning applications and approvals</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Permits &amp; Fees</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Building Permit Fees</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Fees for general building permits</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Permits &amp; Fees</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Impact Fees (School</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Parks)</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Fees levied by local authorities for new development</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Studies &amp; Reports</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Appraisal &amp; Market Study</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>Valuation report and market demand analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Taxes &amp; Insurance</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Property Taxes (During Construction)</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Property taxes paid during the development phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Taxes &amp; Insurance</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Builder's Risk Insurance</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Insurance coverage for the project during construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Taxes &amp; Insurance</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>General Liability Insurance (Construction)</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>Liability insurance during construction period</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Developer &amp; CM Fees</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Developer Fee (Deferred/Paid)</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Compensation for developer's services and risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Developer &amp; CM Fees</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Construction Management Fee</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Fee for construction manager's oversight</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Loan Costs</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Loan Origination Fee</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>600000</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Fee paid to lender at loan closing (e.g.</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>1.5% of $40M loan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Loan Costs</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Loan Underwriting &amp; Legal Fees</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Lender's legal and processing costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Reserves</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Construction Loan Interest Reserve</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Funds reserved to pay interest during construction period</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Lease-Up Costs</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Pre-Opening Marketing &amp; Advertising</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Costs for initial marketing and branding before opening</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Lease-Up Costs</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Leasing Commission Reserve</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>350000</v>
+      </c>
+      <c r="F51" s="9" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Funds for leasing agent commissions</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Operating Reserves</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Operating Deficit Reserve (Post-Construction)</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>Reserve for potential operating losses during initial stabilization</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>FF&amp;E</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>FF&amp;E (Clubhouse</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Office Equipment)</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>fixtures</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>and equipment for common areas and leasing office</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Contingency</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Hard Cost Contingency</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Hard Cost Contingency (5%)</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>2065000</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Reserve for unforeseen hard cost overruns (5% of $41.3M hard costs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Contingency</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Soft Cost Contingency</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Soft Cost Contingency (Approx 3%)</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>460000</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Reserve for unforeseen soft cost overruns</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K55"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>